--- a/data/trans_camb/P19-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 9,64</t>
+          <t>-3,21; 10,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 9,28</t>
+          <t>-3,9; 9,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 11,0</t>
+          <t>-1,13; 11,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 4,93</t>
+          <t>-10,88; 5,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 8,8</t>
+          <t>-6,54; 9,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 12,01</t>
+          <t>-2,25; 11,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 6,15</t>
+          <t>-4,07; 5,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 7,35</t>
+          <t>-2,27; 7,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 9,97</t>
+          <t>0,94; 10,06</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 33,16</t>
+          <t>-9,45; 36,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 32,76</t>
+          <t>-10,92; 31,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 38,64</t>
+          <t>-3,42; 38,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,07; 12,54</t>
+          <t>-24,14; 14,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 24,11</t>
+          <t>-14,4; 26,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 32,36</t>
+          <t>-4,82; 32,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 18,62</t>
+          <t>-10,78; 17,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 22,47</t>
+          <t>-5,81; 23,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 30,07</t>
+          <t>2,51; 30,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 9,15</t>
+          <t>-5,93; 8,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 7,24</t>
+          <t>-5,54; 7,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 5,66</t>
+          <t>-7,42; 6,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 7,85</t>
+          <t>-6,95; 9,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 9,16</t>
+          <t>-4,86; 9,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 9,19</t>
+          <t>-4,26; 9,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 5,85</t>
+          <t>-4,29; 5,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 6,39</t>
+          <t>-4,39; 5,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 4,91</t>
+          <t>-4,21; 5,51</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 34,29</t>
+          <t>-16,82; 30,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 26,13</t>
+          <t>-16,62; 26,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 20,32</t>
+          <t>-20,99; 22,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 21,61</t>
+          <t>-15,69; 24,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 25,06</t>
+          <t>-10,9; 26,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 25,31</t>
+          <t>-9,71; 27,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 17,29</t>
+          <t>-11,33; 17,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 19,37</t>
+          <t>-11,66; 17,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 15,13</t>
+          <t>-10,96; 16,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 1,35</t>
+          <t>-7,93; 2,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 8,2</t>
+          <t>-3,26; 7,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 7,58</t>
+          <t>-17,37; 8,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 15,75</t>
+          <t>-4,36; 14,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 14,85</t>
+          <t>-5,71; 14,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 9,87</t>
+          <t>-9,01; 9,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 4,64</t>
+          <t>-4,97; 4,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 8,04</t>
+          <t>-1,93; 8,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 6,28</t>
+          <t>-18,07; 6,08</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,85; 5,95</t>
+          <t>-29,9; 9,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 38,05</t>
+          <t>-11,82; 34,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,83; 31,45</t>
+          <t>-68,27; 34,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 61,67</t>
+          <t>-11,49; 55,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 59,61</t>
+          <t>-17,29; 55,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 40,64</t>
+          <t>-24,98; 36,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 19,22</t>
+          <t>-17,52; 18,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 34,06</t>
+          <t>-7,28; 33,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,28; 25,15</t>
+          <t>-69,19; 24,53</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,88; -0,12</t>
+          <t>-6,85; -0,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 7,57</t>
+          <t>0,54; 7,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 3,02</t>
+          <t>-3,96; 3,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 0,14</t>
+          <t>-9,56; 0,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 8,02</t>
+          <t>-1,88; 7,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 5,42</t>
+          <t>-19,69; 5,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,44; -0,54</t>
+          <t>-6,18; -0,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,11</t>
+          <t>1,33; 7,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 3,07</t>
+          <t>-11,1; 2,94</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,72; -0,5</t>
+          <t>-28,69; -2,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,0; 36,46</t>
+          <t>2,24; 36,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 14,42</t>
+          <t>-16,91; 16,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,28; 0,56</t>
+          <t>-27,32; 1,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 27,64</t>
+          <t>-5,54; 25,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,04; 17,57</t>
+          <t>-53,75; 16,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,47; -2,22</t>
+          <t>-22,48; -2,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,98; 28,58</t>
+          <t>4,75; 28,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 12,3</t>
+          <t>-40,26; 11,2</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 7,26</t>
+          <t>-3,99; 7,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 10,46</t>
+          <t>0,26; 11,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 6,37</t>
+          <t>-5,32; 6,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 3,74</t>
+          <t>-6,76; 3,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 5,85</t>
+          <t>-4,63; 5,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 3,27</t>
+          <t>-13,13; 2,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 3,25</t>
+          <t>-4,2; 3,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 5,54</t>
+          <t>-1,89; 5,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 3,5</t>
+          <t>-8,69; 3,01</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,98; 47,09</t>
+          <t>-17,72; 49,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 67,23</t>
+          <t>1,31; 74,71</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 40,39</t>
+          <t>-25,01; 39,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 13,27</t>
+          <t>-20,34; 13,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 21,01</t>
+          <t>-14,12; 21,56</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-39,95; 13,18</t>
+          <t>-41,58; 10,56</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 13,43</t>
+          <t>-15,27; 12,91</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 23,54</t>
+          <t>-6,92; 23,7</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 14,89</t>
+          <t>-31,93; 12,7</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,87; 17,06</t>
+          <t>2,02; 17,9</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10,21; 24,98</t>
+          <t>10,74; 25,62</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 18,94</t>
+          <t>-3,36; 20,35</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 3,83</t>
+          <t>-3,43; 3,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,23; 8,77</t>
+          <t>1,22; 9,1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 0,11</t>
+          <t>-7,82; 0,04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,53</t>
+          <t>-1,4; 5,51</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,02</t>
+          <t>3,72; 11,01</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 2,96</t>
+          <t>-5,43; 2,46</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7,48; 85,0</t>
+          <t>7,74; 87,95</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>37,37; 121,56</t>
+          <t>37,67; 126,13</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 84,88</t>
+          <t>-12,33; 92,58</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 15,07</t>
+          <t>-12,42; 14,51</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,4; 35,36</t>
+          <t>4,41; 36,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-27,72; 0,45</t>
+          <t>-27,51; 0,24</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 22,4</t>
+          <t>-5,2; 23,1</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15,45; 43,86</t>
+          <t>13,17; 44,84</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 11,66</t>
+          <t>-19,89; 9,91</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,05</t>
+          <t>-2,56; 1,78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,42</t>
+          <t>2,02; 6,44</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 3,3</t>
+          <t>-6,57; 3,22</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,37</t>
+          <t>-3,06; 1,47</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,29</t>
+          <t>1,1; 5,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 1,77</t>
+          <t>-7,06; 1,93</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,94</t>
+          <t>-2,2; 1,01</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,27</t>
+          <t>2,03; 5,13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 2,08</t>
+          <t>-4,4; 1,78</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 8,66</t>
+          <t>-10,03; 7,52</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>8,06; 26,88</t>
+          <t>7,39; 27,13</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 13,7</t>
+          <t>-25,87; 13,09</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 4,6</t>
+          <t>-9,45; 4,74</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,5; 17,44</t>
+          <t>3,5; 18,41</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 5,46</t>
+          <t>-22,08; 6,14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 3,4</t>
+          <t>-7,53; 3,66</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>7,83; 19,17</t>
+          <t>7,03; 18,93</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 7,55</t>
+          <t>-15,94; 6,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,79</t>
+          <t>5,56</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 10,34</t>
+          <t>-3,26; 9,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 9,13</t>
+          <t>-3,86; 9,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 11,39</t>
+          <t>-0,55; 11,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 5,15</t>
+          <t>-11,17; 4,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 9,3</t>
+          <t>-6,76; 8,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 11,68</t>
+          <t>-3,11; 10,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 5,82</t>
+          <t>-4,15; 5,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 7,75</t>
+          <t>-2,34; 7,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 10,06</t>
+          <t>0,95; 9,82</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 36,34</t>
+          <t>-9,43; 33,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 31,28</t>
+          <t>-10,92; 33,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 38,95</t>
+          <t>-1,84; 39,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 14,03</t>
+          <t>-25,12; 12,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 26,13</t>
+          <t>-15,57; 23,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 32,03</t>
+          <t>-6,87; 30,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 17,5</t>
+          <t>-10,92; 17,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 23,83</t>
+          <t>-6,15; 22,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 30,71</t>
+          <t>2,55; 30,2</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>-0,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 8,67</t>
+          <t>-5,51; 8,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 7,61</t>
+          <t>-6,41; 8,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 6,28</t>
+          <t>-7,89; 5,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 9,27</t>
+          <t>-6,7; 8,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 9,73</t>
+          <t>-5,13; 8,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 9,55</t>
+          <t>-4,22; 8,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 5,76</t>
+          <t>-4,54; 5,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 5,96</t>
+          <t>-4,1; 6,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 5,51</t>
+          <t>-4,58; 5,08</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-2,09%</t>
+          <t>-4,5%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>-0,22%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 30,89</t>
+          <t>-15,92; 31,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 26,64</t>
+          <t>-18,63; 30,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 22,9</t>
+          <t>-22,45; 18,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 24,97</t>
+          <t>-15,77; 25,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 26,63</t>
+          <t>-11,68; 24,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 27,01</t>
+          <t>-9,83; 24,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 17,04</t>
+          <t>-11,94; 17,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 17,72</t>
+          <t>-10,79; 19,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 16,87</t>
+          <t>-11,98; 15,0</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-5,12</t>
+          <t>6,03</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,19</t>
+          <t>4,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 2,11</t>
+          <t>-7,86; 1,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 7,57</t>
+          <t>-2,7; 7,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 8,17</t>
+          <t>0,49; 12,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 14,22</t>
+          <t>-3,04; 14,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 14,02</t>
+          <t>-7,03; 14,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 9,56</t>
+          <t>-7,18; 10,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 4,26</t>
+          <t>-5,04; 4,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 8,05</t>
+          <t>-2,14; 7,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 6,08</t>
+          <t>0,3; 10,13</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-20,93%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-16,19%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 9,07</t>
+          <t>-29,83; 9,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 34,17</t>
+          <t>-10,1; 36,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,27; 34,88</t>
+          <t>1,5; 55,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 55,91</t>
+          <t>-9,09; 58,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 55,74</t>
+          <t>-20,1; 57,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 36,63</t>
+          <t>-20,09; 40,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 18,13</t>
+          <t>-17,97; 17,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 33,21</t>
+          <t>-7,5; 34,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,19; 24,53</t>
+          <t>0,72; 42,29</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,04</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,06</t>
+          <t>1,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,85; -0,37</t>
+          <t>-6,79; -0,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 7,5</t>
+          <t>0,16; 6,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 3,27</t>
+          <t>-4,44; 2,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 0,32</t>
+          <t>-9,26; 0,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 7,81</t>
+          <t>-1,68; 7,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 5,19</t>
+          <t>-2,35; 6,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,18; -0,65</t>
+          <t>-6,3; -0,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,05</t>
+          <t>1,01; 6,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 2,94</t>
+          <t>-1,64; 4,04</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-2,33%</t>
+          <t>-2,72%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-12,54%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-4,09%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,69; -2,08</t>
+          <t>-27,88; -1,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 36,61</t>
+          <t>0,89; 33,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 16,12</t>
+          <t>-18,27; 12,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 1,26</t>
+          <t>-26,97; 0,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 25,72</t>
+          <t>-4,65; 27,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,75; 16,59</t>
+          <t>-6,66; 21,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,48; -2,61</t>
+          <t>-22,76; -2,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,75; 28,52</t>
+          <t>3,68; 28,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 11,2</t>
+          <t>-5,95; 16,76</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>-2,08</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,3</t>
+          <t>-7,51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,59</t>
+          <t>-5,61</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 7,24</t>
+          <t>-3,82; 7,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,26; 11,18</t>
+          <t>0,16; 10,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 6,19</t>
+          <t>-7,54; 3,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 3,67</t>
+          <t>-6,7; 3,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 5,85</t>
+          <t>-4,58; 5,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 2,95</t>
+          <t>-12,12; -2,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 3,07</t>
+          <t>-4,33; 3,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 5,56</t>
+          <t>-1,67; 5,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 3,01</t>
+          <t>-9,66; -2,18</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>-11,22%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-20,71%</t>
+          <t>-24,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-13,89%</t>
+          <t>-21,66%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 49,0</t>
+          <t>-17,33; 44,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1,31; 74,71</t>
+          <t>0,79; 70,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-25,01; 39,78</t>
+          <t>-35,83; 21,55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 13,5</t>
+          <t>-20,19; 12,9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 21,56</t>
+          <t>-14,3; 20,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-41,58; 10,56</t>
+          <t>-35,83; -10,67</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 12,91</t>
+          <t>-15,44; 13,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 23,7</t>
+          <t>-6,12; 22,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 12,7</t>
+          <t>-33,76; -9,28</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7,71</t>
+          <t>6,86</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,96</t>
+          <t>-3,89</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>-1,59</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,02; 17,9</t>
+          <t>2,36; 17,71</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10,74; 25,62</t>
+          <t>9,74; 25,48</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 20,35</t>
+          <t>-3,32; 18,27</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 3,58</t>
+          <t>-3,61; 3,65</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,22; 9,1</t>
+          <t>1,46; 8,76</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 0,04</t>
+          <t>-7,55; 0,07</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 5,51</t>
+          <t>-1,14; 5,33</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,72; 11,01</t>
+          <t>4,32; 11,34</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 2,46</t>
+          <t>-5,5; 1,98</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-14,96%</t>
+          <t>-14,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-4,89%</t>
+          <t>-6,13%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7,74; 87,95</t>
+          <t>8,62; 87,74</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>37,67; 126,13</t>
+          <t>34,97; 125,22</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 92,58</t>
+          <t>-13,57; 86,99</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 14,51</t>
+          <t>-12,87; 14,58</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,41; 36,79</t>
+          <t>5,03; 34,68</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 0,24</t>
+          <t>-26,83; 0,32</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 23,1</t>
+          <t>-4,18; 21,68</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>13,17; 44,84</t>
+          <t>15,79; 46,45</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 9,91</t>
+          <t>-20,18; 8,04</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>0,7</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,78</t>
+          <t>-2,49; 1,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,44</t>
+          <t>1,74; 6,42</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 3,22</t>
+          <t>-0,77; 3,74</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,47</t>
+          <t>-3,38; 1,16</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,54</t>
+          <t>0,97; 5,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 1,93</t>
+          <t>-2,08; 2,0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,01</t>
+          <t>-2,08; 0,96</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,13</t>
+          <t>2,15; 5,2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,78</t>
+          <t>-0,8; 2,42</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-4,61%</t>
+          <t>-0,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-2,05%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 7,52</t>
+          <t>-9,63; 7,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7,39; 27,13</t>
+          <t>6,79; 26,76</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 13,09</t>
+          <t>-2,81; 15,71</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 4,74</t>
+          <t>-10,19; 3,81</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,5; 18,41</t>
+          <t>2,99; 17,7</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 6,14</t>
+          <t>-6,42; 6,54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 3,66</t>
+          <t>-7,25; 3,48</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>7,03; 18,93</t>
+          <t>7,44; 18,91</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 6,35</t>
+          <t>-2,75; 8,76</t>
         </is>
       </c>
     </row>
